--- a/Project/outputs/tables/table_spillover_war.xlsx
+++ b/Project/outputs/tables/table_spillover_war.xlsx
@@ -436,19 +436,19 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>CAC40</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>FTSE100</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DAX</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Nikkei</t>
@@ -456,17 +456,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>HangSeng</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>CSI300</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -482,133 +482,133 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.89</v>
+        <v>21.51</v>
       </c>
       <c r="C2" t="n">
-        <v>11.83</v>
+        <v>12.5</v>
       </c>
       <c r="D2" t="n">
-        <v>9.41</v>
+        <v>22.23</v>
       </c>
       <c r="E2" t="n">
-        <v>7.99</v>
+        <v>23.03</v>
       </c>
       <c r="F2" t="n">
-        <v>4.86</v>
+        <v>3.95</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4</v>
+        <v>4.97</v>
       </c>
       <c r="H2" t="n">
-        <v>1.32</v>
+        <v>2.27</v>
       </c>
       <c r="I2" t="n">
-        <v>21.29</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>11.54</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.68</v>
+        <v>11.77</v>
       </c>
       <c r="C3" t="n">
-        <v>27.51</v>
+        <v>19.1</v>
       </c>
       <c r="D3" t="n">
-        <v>18.32</v>
+        <v>27.78</v>
       </c>
       <c r="E3" t="n">
-        <v>20.04</v>
+        <v>23.93</v>
       </c>
       <c r="F3" t="n">
-        <v>5.19</v>
+        <v>0.83</v>
       </c>
       <c r="G3" t="n">
-        <v>3.55</v>
+        <v>8.18</v>
       </c>
       <c r="H3" t="n">
-        <v>1.36</v>
+        <v>2.07</v>
       </c>
       <c r="I3" t="n">
-        <v>10.35</v>
+        <v>6.34</v>
       </c>
       <c r="J3" t="n">
-        <v>11.71</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.49</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>22.88</v>
+        <v>15.15</v>
       </c>
       <c r="D4" t="n">
-        <v>27.23</v>
+        <v>31.25</v>
       </c>
       <c r="E4" t="n">
-        <v>15.85</v>
+        <v>30.65</v>
       </c>
       <c r="F4" t="n">
-        <v>4.74</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>3.46</v>
+        <v>5.35</v>
       </c>
       <c r="H4" t="n">
-        <v>1.07</v>
+        <v>2.77</v>
       </c>
       <c r="I4" t="n">
-        <v>10.28</v>
+        <v>4.03</v>
       </c>
       <c r="J4" t="n">
-        <v>9.34</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.99</v>
+        <v>7.46</v>
       </c>
       <c r="C5" t="n">
-        <v>24.43</v>
+        <v>12.71</v>
       </c>
       <c r="D5" t="n">
-        <v>16.8</v>
+        <v>24.55</v>
       </c>
       <c r="E5" t="n">
-        <v>28.87</v>
+        <v>34.34</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>2.67</v>
+        <v>7.03</v>
       </c>
       <c r="H5" t="n">
-        <v>1.33</v>
+        <v>4.63</v>
       </c>
       <c r="I5" t="n">
-        <v>9.91</v>
+        <v>7.97</v>
       </c>
       <c r="J5" t="n">
-        <v>8.66</v>
+        <v>16.91</v>
       </c>
     </row>
     <row r="6">
@@ -618,133 +618,133 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.29</v>
+        <v>20.45</v>
       </c>
       <c r="C6" t="n">
-        <v>11.44</v>
+        <v>2.28</v>
       </c>
       <c r="D6" t="n">
-        <v>6.89</v>
+        <v>12.01</v>
       </c>
       <c r="E6" t="n">
-        <v>5.5</v>
+        <v>8.41</v>
       </c>
       <c r="F6" t="n">
-        <v>52.94</v>
+        <v>51.89</v>
       </c>
       <c r="G6" t="n">
-        <v>7.86</v>
+        <v>2.21</v>
       </c>
       <c r="H6" t="n">
-        <v>0.41</v>
+        <v>2.44</v>
       </c>
       <c r="I6" t="n">
-        <v>3.66</v>
+        <v>0.32</v>
       </c>
       <c r="J6" t="n">
-        <v>3.63</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.64</v>
+        <v>9.27</v>
       </c>
       <c r="C7" t="n">
-        <v>7.66</v>
+        <v>15.87</v>
       </c>
       <c r="D7" t="n">
-        <v>9.75</v>
+        <v>18.06</v>
       </c>
       <c r="E7" t="n">
-        <v>5.83</v>
+        <v>17.65</v>
       </c>
       <c r="F7" t="n">
-        <v>6.95</v>
+        <v>0.42</v>
       </c>
       <c r="G7" t="n">
-        <v>35.08</v>
+        <v>22.41</v>
       </c>
       <c r="H7" t="n">
-        <v>6.3</v>
+        <v>6.35</v>
       </c>
       <c r="I7" t="n">
-        <v>14.79</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>4.72</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.12</v>
+        <v>1.82</v>
       </c>
       <c r="C8" t="n">
-        <v>4.46</v>
+        <v>10.34</v>
       </c>
       <c r="D8" t="n">
-        <v>4.35</v>
+        <v>16.42</v>
       </c>
       <c r="E8" t="n">
-        <v>5.3</v>
+        <v>17.98</v>
       </c>
       <c r="F8" t="n">
-        <v>0.47</v>
+        <v>1.12</v>
       </c>
       <c r="G8" t="n">
-        <v>10.45</v>
+        <v>13.09</v>
       </c>
       <c r="H8" t="n">
-        <v>64.04000000000001</v>
+        <v>24.12</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>15.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.82</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.08</v>
+        <v>2.32</v>
       </c>
       <c r="C9" t="n">
-        <v>10.93</v>
+        <v>8.06</v>
       </c>
       <c r="D9" t="n">
-        <v>9.199999999999999</v>
+        <v>12.59</v>
       </c>
       <c r="E9" t="n">
-        <v>8.800000000000001</v>
+        <v>13.64</v>
       </c>
       <c r="F9" t="n">
-        <v>2.83</v>
+        <v>1.83</v>
       </c>
       <c r="G9" t="n">
-        <v>5.38</v>
+        <v>8.08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>13.44</v>
       </c>
       <c r="I9" t="n">
-        <v>36.99</v>
+        <v>40.03</v>
       </c>
       <c r="J9" t="n">
-        <v>9.640000000000001</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7.64</v>
+        <v>9.81</v>
       </c>
       <c r="C10" t="n">
-        <v>9.06</v>
+        <v>10.11</v>
       </c>
       <c r="D10" t="n">
-        <v>9.1</v>
+        <v>8.59</v>
       </c>
       <c r="E10" t="n">
-        <v>8.890000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>5.88</v>
+        <v>6.01</v>
       </c>
       <c r="G10" t="n">
-        <v>8.119999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>4.49</v>
+        <v>9.49</v>
       </c>
       <c r="I10" t="n">
-        <v>7.88</v>
+        <v>7.5</v>
       </c>
       <c r="J10" t="n">
-        <v>61.06</v>
+        <v>69.42</v>
       </c>
     </row>
   </sheetData>
